--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0001T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0001T0006Z000C1N37_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>66.48061662652512</v>
+        <v>10.80310020181033</v>
       </c>
       <c r="D2" t="n">
-        <v>66.85888155905567</v>
+        <v>10.86456825334655</v>
       </c>
       <c r="E2" t="n">
-        <v>20.25627105287937</v>
+        <v>3.291644046092898</v>
       </c>
       <c r="F2" t="n">
-        <v>14.38564062809584</v>
+        <v>2.337666602065574</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.04353582823701</v>
+        <v>3.744574572088514</v>
       </c>
       <c r="D3" t="n">
-        <v>31.88253061848011</v>
+        <v>5.180911225503019</v>
       </c>
       <c r="E3" t="n">
-        <v>20.25627105287937</v>
+        <v>3.291644046092898</v>
       </c>
       <c r="F3" t="n">
-        <v>14.38564062809584</v>
+        <v>2.337666602065574</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>65.53078671086985</v>
+        <v>10.64875284051635</v>
       </c>
       <c r="D4" t="n">
-        <v>45.66245725346548</v>
+        <v>7.420149303688142</v>
       </c>
       <c r="E4" t="n">
-        <v>20.25627105287937</v>
+        <v>3.291644046092898</v>
       </c>
       <c r="F4" t="n">
-        <v>14.38564062809584</v>
+        <v>2.337666602065574</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
